--- a/artfynd/A 73873-2021 artfynd.xlsx
+++ b/artfynd/A 73873-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73873-2021 artfynd.xlsx
+++ b/artfynd/A 73873-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102551220</v>
+        <v>102551296</v>
       </c>
       <c r="B2" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714642.4813486956</v>
+        <v>714458</v>
       </c>
       <c r="R2" t="n">
-        <v>7401270.577526907</v>
+        <v>7400964</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102551296</v>
+        <v>102551330</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>714457.465145031</v>
+        <v>714332</v>
       </c>
       <c r="R3" t="n">
-        <v>7400964.220492867</v>
+        <v>7401029</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102551218</v>
+        <v>102551331</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714748.0361021785</v>
+        <v>714385</v>
       </c>
       <c r="R4" t="n">
-        <v>7400990.870692059</v>
+        <v>7401086</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102551212</v>
+        <v>102551332</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714755.4220566589</v>
+        <v>714436</v>
       </c>
       <c r="R5" t="n">
-        <v>7400983.083257046</v>
+        <v>7400984</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102551321</v>
+        <v>102551333</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>714820.0748905328</v>
+        <v>714493</v>
       </c>
       <c r="R6" t="n">
-        <v>7401160.982755738</v>
+        <v>7400941</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102551262</v>
+        <v>102551205</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>714707.626508364</v>
+        <v>714384</v>
       </c>
       <c r="R7" t="n">
-        <v>7401268.493437374</v>
+        <v>7401082</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,19 +1228,14 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>gamla hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102551207</v>
+        <v>102551192</v>
       </c>
       <c r="B8" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208255</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>714549.003317418</v>
+        <v>714444</v>
       </c>
       <c r="R8" t="n">
-        <v>7400915.199469088</v>
+        <v>7401007</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,19 +1330,14 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-05</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102551333</v>
+        <v>102551207</v>
       </c>
       <c r="B9" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>208255</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>714492.7911224457</v>
+        <v>714549</v>
       </c>
       <c r="R9" t="n">
-        <v>7400940.687818963</v>
+        <v>7400915</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,22 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102551302</v>
+        <v>102551220</v>
       </c>
       <c r="B10" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>714658.6772609183</v>
+        <v>714642</v>
       </c>
       <c r="R10" t="n">
-        <v>7400873.967854743</v>
+        <v>7401271</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,19 +1529,9 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102551320</v>
+        <v>102551286</v>
       </c>
       <c r="B11" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>714649.5776799488</v>
+        <v>714835</v>
       </c>
       <c r="R11" t="n">
-        <v>7401276.706692797</v>
+        <v>7401156</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,19 +1626,9 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102551332</v>
+        <v>102551287</v>
       </c>
       <c r="B12" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>714436.3803109112</v>
+        <v>714817</v>
       </c>
       <c r="R12" t="n">
-        <v>7400984.084024782</v>
+        <v>7401096</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,22 +1720,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102551287</v>
+        <v>102551262</v>
       </c>
       <c r="B13" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>714816.7920579572</v>
+        <v>714708</v>
       </c>
       <c r="R13" t="n">
-        <v>7401095.808731605</v>
+        <v>7401268</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,19 +1820,9 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102551286</v>
+        <v>102551320</v>
       </c>
       <c r="B14" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>714834.8042736114</v>
+        <v>714650</v>
       </c>
       <c r="R14" t="n">
-        <v>7401156.159126271</v>
+        <v>7401277</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2092,19 +1917,9 @@
           <t>2022-05-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,6 +1943,496 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>102551321</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>På eller i anslutning till Stormyren Vajkijaure, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>714820</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7401161</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>102551302</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>På eller i anslutning till Stormyren Vajkijaure, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>714659</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7400874</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>102551176</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>På eller i anslutning till Stormyren Vajkijaure, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>714634</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7401053</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>tupp</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>102551218</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>På eller i anslutning till Stormyren Vajkijaure, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>714748</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7400991</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>102551212</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>På eller i anslutning till Stormyren Vajkijaure, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>714755</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7400983</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-05-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73873-2021 artfynd.xlsx
+++ b/artfynd/A 73873-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551220</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551286</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551287</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551262</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551320</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551330</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551331</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551332</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551333</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551302</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551205</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551176</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551192</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551207</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551218</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,8 +2523,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102551212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>